--- a/Calificaciones_1s_2025.xlsx
+++ b/Calificaciones_1s_2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Omar\Documents\Cursos\Física Computacional III para Astrofísica\2025_1s\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92A8B16F-C7A6-47D5-B61A-58918C3B92A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4C36BA7-CE02-493D-9C00-442424B913DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-104" yWindow="-104" windowWidth="22326" windowHeight="12050" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
   <si>
     <t>11/04/2025 13:25:09</t>
   </si>
@@ -264,13 +264,16 @@
   </si>
   <si>
     <t>PROMEDIO</t>
+  </si>
+  <si>
+    <t>Situación Final</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -285,6 +288,7 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -308,11 +312,13 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -324,6 +330,15 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -587,7 +602,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -638,16 +653,26 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -670,22 +695,30 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -697,7 +730,65 @@
     <cellStyle name="Normal 5" xfId="4" xr:uid="{2C655FE6-0C66-40EF-AB21-F1FDA2CBF38B}"/>
     <cellStyle name="Normal 6" xfId="5" xr:uid="{8502967F-F2F6-4CD0-9005-23248AD21CC2}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="7">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEE0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00E668"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFEE0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFEE0000"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -956,7 +1047,7 @@
     <col min="5" max="5" width="7.88671875" customWidth="1"/>
     <col min="6" max="6" width="9.21875" customWidth="1"/>
     <col min="7" max="7" width="6.44140625" customWidth="1"/>
-    <col min="8" max="8" width="10.109375" customWidth="1"/>
+    <col min="8" max="8" width="13.77734375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.6640625" customWidth="1"/>
     <col min="10" max="10" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8.88671875" customWidth="1"/>
@@ -966,10 +1057,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="39.75" customHeight="1">
-      <c r="A1" s="24"/>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="26"/>
+      <c r="A1" s="26"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="28"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -981,27 +1072,27 @@
       <c r="M1" s="1"/>
     </row>
     <row r="2" spans="1:13" ht="19.45" customHeight="1">
-      <c r="A2" s="27"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="29"/>
+      <c r="A2" s="29"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="31"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-      <c r="I2" s="33" t="s">
+      <c r="I2" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="34"/>
-      <c r="K2" s="35"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="37"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" ht="3.75" customHeight="1">
-      <c r="A3" s="30"/>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="32"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="34"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
@@ -1028,19 +1119,19 @@
       <c r="M4" s="1"/>
     </row>
     <row r="5" spans="1:13" ht="15.7" customHeight="1">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="37" t="s">
+      <c r="B5" s="37"/>
+      <c r="C5" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="35"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="37"/>
       <c r="J5" s="2" t="s">
         <v>3</v>
       </c>
@@ -1051,23 +1142,23 @@
       <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:13" ht="15.7" customHeight="1">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="35"/>
-      <c r="C6" s="37" t="s">
+      <c r="B6" s="37"/>
+      <c r="C6" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="34"/>
-      <c r="I6" s="34"/>
-      <c r="J6" s="34"/>
-      <c r="K6" s="34"/>
-      <c r="L6" s="34"/>
-      <c r="M6" s="35"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="36"/>
+      <c r="J6" s="36"/>
+      <c r="K6" s="36"/>
+      <c r="L6" s="36"/>
+      <c r="M6" s="37"/>
     </row>
     <row r="7" spans="1:13" ht="4.5" customHeight="1">
       <c r="A7" s="1"/>
@@ -1100,17 +1191,19 @@
       <c r="E8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="21"/>
-      <c r="J8" s="22"/>
-      <c r="K8" s="22"/>
-      <c r="L8" s="23"/>
+      <c r="H8" s="46" t="s">
+        <v>77</v>
+      </c>
+      <c r="I8" s="40"/>
+      <c r="J8" s="41"/>
+      <c r="K8" s="41"/>
+      <c r="L8" s="42"/>
       <c r="M8" s="16"/>
     </row>
     <row r="9" spans="1:13" ht="19.45" customHeight="1">
@@ -1123,17 +1216,27 @@
       <c r="C9" s="9">
         <v>65</v>
       </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="38">
+      <c r="D9" s="9">
+        <v>50</v>
+      </c>
+      <c r="E9" s="9">
         <v>34</v>
       </c>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="20"/>
+      <c r="F9" s="44">
+        <v>11</v>
+      </c>
+      <c r="G9" s="47">
+        <f>0.3*(C9+D9)/2+0.35*E9+0.35*F9</f>
+        <v>33</v>
+      </c>
+      <c r="H9" s="48" t="str">
+        <f>IF(G9&gt;=40,"Aprobado/a",IF(G9&gt;=30,"Examen PES","Reprobado/a"))</f>
+        <v>Examen PES</v>
+      </c>
+      <c r="I9" s="23"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="25"/>
       <c r="M9" s="16"/>
     </row>
     <row r="10" spans="1:13" ht="19.45" customHeight="1">
@@ -1146,17 +1249,27 @@
       <c r="C10" s="9">
         <v>37</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="38">
+      <c r="D10" s="9">
+        <v>10</v>
+      </c>
+      <c r="E10" s="9">
         <v>13</v>
       </c>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="20"/>
+      <c r="F10" s="44">
+        <v>12</v>
+      </c>
+      <c r="G10" s="47">
+        <f t="shared" ref="G10:G39" si="0">0.3*(C10+D10)/2+0.35*E10+0.35*F10</f>
+        <v>15.799999999999999</v>
+      </c>
+      <c r="H10" s="48" t="str">
+        <f t="shared" ref="H10:H39" si="1">IF(G10&gt;=40,"Aprobado/a",IF(G10&gt;=30,"Examen PES","Reprobado/a"))</f>
+        <v>Reprobado/a</v>
+      </c>
+      <c r="I10" s="23"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="25"/>
       <c r="M10" s="16"/>
     </row>
     <row r="11" spans="1:13" ht="19.45" customHeight="1">
@@ -1169,17 +1282,27 @@
       <c r="C11" s="14">
         <v>68</v>
       </c>
-      <c r="D11" s="14"/>
-      <c r="E11" s="38">
+      <c r="D11" s="14">
+        <v>50</v>
+      </c>
+      <c r="E11" s="9">
         <v>54</v>
       </c>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="20"/>
+      <c r="F11" s="45">
+        <v>57</v>
+      </c>
+      <c r="G11" s="47">
+        <f t="shared" si="0"/>
+        <v>56.55</v>
+      </c>
+      <c r="H11" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Aprobado/a</v>
+      </c>
+      <c r="I11" s="23"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="25"/>
       <c r="M11" s="16"/>
     </row>
     <row r="12" spans="1:13" ht="19.45" customHeight="1">
@@ -1192,17 +1315,27 @@
       <c r="C12" s="9">
         <v>60</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="38">
+      <c r="D12" s="9">
+        <v>70</v>
+      </c>
+      <c r="E12" s="9">
         <v>33</v>
       </c>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="20"/>
+      <c r="F12" s="44">
+        <v>40</v>
+      </c>
+      <c r="G12" s="47">
+        <f t="shared" si="0"/>
+        <v>45.05</v>
+      </c>
+      <c r="H12" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Aprobado/a</v>
+      </c>
+      <c r="I12" s="23"/>
+      <c r="J12" s="24"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="25"/>
       <c r="M12" s="16"/>
     </row>
     <row r="13" spans="1:13" ht="19.45" customHeight="1">
@@ -1215,17 +1348,27 @@
       <c r="C13" s="9">
         <v>60</v>
       </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="38">
+      <c r="D13" s="9">
+        <v>50</v>
+      </c>
+      <c r="E13" s="9">
         <v>40</v>
       </c>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="20"/>
+      <c r="F13" s="44">
+        <v>37</v>
+      </c>
+      <c r="G13" s="47">
+        <f t="shared" si="0"/>
+        <v>43.45</v>
+      </c>
+      <c r="H13" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Aprobado/a</v>
+      </c>
+      <c r="I13" s="23"/>
+      <c r="J13" s="24"/>
+      <c r="K13" s="24"/>
+      <c r="L13" s="25"/>
       <c r="M13" s="16"/>
     </row>
     <row r="14" spans="1:13" ht="19.45" customHeight="1">
@@ -1238,17 +1381,27 @@
       <c r="C14" s="9">
         <v>40</v>
       </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="38">
+      <c r="D14" s="9">
+        <v>55</v>
+      </c>
+      <c r="E14" s="9">
         <v>26</v>
       </c>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="20"/>
+      <c r="F14" s="44">
+        <v>28</v>
+      </c>
+      <c r="G14" s="47">
+        <f t="shared" si="0"/>
+        <v>33.15</v>
+      </c>
+      <c r="H14" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Examen PES</v>
+      </c>
+      <c r="I14" s="23"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="25"/>
       <c r="M14" s="16"/>
     </row>
     <row r="15" spans="1:13" ht="19.45" customHeight="1">
@@ -1261,17 +1414,27 @@
       <c r="C15" s="9">
         <v>70</v>
       </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="39">
+      <c r="D15" s="9">
+        <v>67</v>
+      </c>
+      <c r="E15" s="18">
         <v>34</v>
       </c>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="19"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="20"/>
+      <c r="F15" s="44">
+        <v>46</v>
+      </c>
+      <c r="G15" s="47">
+        <f t="shared" si="0"/>
+        <v>48.55</v>
+      </c>
+      <c r="H15" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Aprobado/a</v>
+      </c>
+      <c r="I15" s="23"/>
+      <c r="J15" s="24"/>
+      <c r="K15" s="24"/>
+      <c r="L15" s="25"/>
       <c r="M15" s="16"/>
     </row>
     <row r="16" spans="1:13" ht="19.45" customHeight="1">
@@ -1284,17 +1447,27 @@
       <c r="C16" s="9">
         <v>67</v>
       </c>
-      <c r="D16" s="9"/>
-      <c r="E16" s="39">
+      <c r="D16" s="9">
+        <v>53</v>
+      </c>
+      <c r="E16" s="18">
         <v>22</v>
       </c>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="20"/>
+      <c r="F16" s="44">
+        <v>50</v>
+      </c>
+      <c r="G16" s="47">
+        <f t="shared" si="0"/>
+        <v>43.2</v>
+      </c>
+      <c r="H16" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Aprobado/a</v>
+      </c>
+      <c r="I16" s="23"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="25"/>
       <c r="M16" s="16"/>
     </row>
     <row r="17" spans="1:13" ht="19.45" customHeight="1">
@@ -1307,17 +1480,27 @@
       <c r="C17" s="9">
         <v>70</v>
       </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="39">
+      <c r="D17" s="9">
+        <v>65</v>
+      </c>
+      <c r="E17" s="18">
         <v>38</v>
       </c>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="20"/>
+      <c r="F17" s="44">
+        <v>49</v>
+      </c>
+      <c r="G17" s="47">
+        <f t="shared" si="0"/>
+        <v>50.699999999999996</v>
+      </c>
+      <c r="H17" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Aprobado/a</v>
+      </c>
+      <c r="I17" s="23"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="25"/>
       <c r="M17" s="16"/>
     </row>
     <row r="18" spans="1:13" ht="19.45" customHeight="1">
@@ -1330,17 +1513,27 @@
       <c r="C18" s="9">
         <v>68</v>
       </c>
-      <c r="D18" s="9"/>
-      <c r="E18" s="39">
+      <c r="D18" s="9">
+        <v>65</v>
+      </c>
+      <c r="E18" s="18">
         <v>36</v>
       </c>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="20"/>
+      <c r="F18" s="44">
+        <v>55</v>
+      </c>
+      <c r="G18" s="47">
+        <f t="shared" si="0"/>
+        <v>51.8</v>
+      </c>
+      <c r="H18" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Aprobado/a</v>
+      </c>
+      <c r="I18" s="23"/>
+      <c r="J18" s="24"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="25"/>
       <c r="M18" s="16"/>
     </row>
     <row r="19" spans="1:13" ht="19.45" customHeight="1">
@@ -1353,17 +1546,27 @@
       <c r="C19" s="9">
         <v>55</v>
       </c>
-      <c r="D19" s="9"/>
-      <c r="E19" s="38">
+      <c r="D19" s="9">
+        <v>40</v>
+      </c>
+      <c r="E19" s="9">
         <v>14</v>
       </c>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="19"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="20"/>
+      <c r="F19" s="44">
+        <v>12</v>
+      </c>
+      <c r="G19" s="47">
+        <f t="shared" si="0"/>
+        <v>23.349999999999998</v>
+      </c>
+      <c r="H19" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Reprobado/a</v>
+      </c>
+      <c r="I19" s="23"/>
+      <c r="J19" s="24"/>
+      <c r="K19" s="24"/>
+      <c r="L19" s="25"/>
       <c r="M19" s="16"/>
     </row>
     <row r="20" spans="1:13" ht="19.45" customHeight="1">
@@ -1376,15 +1579,25 @@
       <c r="C20" s="9">
         <v>60</v>
       </c>
-      <c r="D20" s="9"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="20"/>
+      <c r="D20" s="9">
+        <v>58</v>
+      </c>
+      <c r="E20" s="9"/>
+      <c r="F20" s="44">
+        <v>12</v>
+      </c>
+      <c r="G20" s="47">
+        <f t="shared" si="0"/>
+        <v>21.9</v>
+      </c>
+      <c r="H20" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Reprobado/a</v>
+      </c>
+      <c r="I20" s="23"/>
+      <c r="J20" s="24"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="25"/>
       <c r="M20" s="16"/>
     </row>
     <row r="21" spans="1:13" ht="19.45" customHeight="1">
@@ -1397,17 +1610,27 @@
       <c r="C21" s="9">
         <v>68</v>
       </c>
-      <c r="D21" s="9"/>
-      <c r="E21" s="38">
+      <c r="D21" s="9">
+        <v>70</v>
+      </c>
+      <c r="E21" s="9">
         <v>44</v>
       </c>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="20"/>
+      <c r="F21" s="44">
+        <v>51</v>
+      </c>
+      <c r="G21" s="47">
+        <f t="shared" si="0"/>
+        <v>53.949999999999989</v>
+      </c>
+      <c r="H21" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Aprobado/a</v>
+      </c>
+      <c r="I21" s="23"/>
+      <c r="J21" s="24"/>
+      <c r="K21" s="24"/>
+      <c r="L21" s="25"/>
       <c r="M21" s="16"/>
     </row>
     <row r="22" spans="1:13" ht="19.45" customHeight="1">
@@ -1420,17 +1643,27 @@
       <c r="C22" s="9">
         <v>55</v>
       </c>
-      <c r="D22" s="9"/>
-      <c r="E22" s="38">
+      <c r="D22" s="9">
+        <v>44</v>
+      </c>
+      <c r="E22" s="9">
         <v>26</v>
       </c>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="18"/>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19"/>
-      <c r="L22" s="20"/>
+      <c r="F22" s="44">
+        <v>33</v>
+      </c>
+      <c r="G22" s="47">
+        <f t="shared" si="0"/>
+        <v>35.5</v>
+      </c>
+      <c r="H22" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Examen PES</v>
+      </c>
+      <c r="I22" s="23"/>
+      <c r="J22" s="24"/>
+      <c r="K22" s="24"/>
+      <c r="L22" s="25"/>
       <c r="M22" s="16"/>
     </row>
     <row r="23" spans="1:13" ht="19.45" customHeight="1">
@@ -1443,17 +1676,27 @@
       <c r="C23" s="9">
         <v>57</v>
       </c>
-      <c r="D23" s="9"/>
-      <c r="E23" s="38">
+      <c r="D23" s="9">
+        <v>65</v>
+      </c>
+      <c r="E23" s="9">
         <v>28</v>
       </c>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19"/>
-      <c r="L23" s="20"/>
+      <c r="F23" s="44">
+        <v>47</v>
+      </c>
+      <c r="G23" s="47">
+        <f t="shared" si="0"/>
+        <v>44.55</v>
+      </c>
+      <c r="H23" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Aprobado/a</v>
+      </c>
+      <c r="I23" s="23"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="25"/>
       <c r="M23" s="16"/>
     </row>
     <row r="24" spans="1:13" ht="19.45" customHeight="1">
@@ -1466,17 +1709,27 @@
       <c r="C24" s="9">
         <v>62</v>
       </c>
-      <c r="D24" s="9"/>
-      <c r="E24" s="38">
+      <c r="D24" s="9">
+        <v>40</v>
+      </c>
+      <c r="E24" s="9">
         <v>10</v>
       </c>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="20"/>
+      <c r="F24" s="44">
+        <v>25</v>
+      </c>
+      <c r="G24" s="47">
+        <f t="shared" si="0"/>
+        <v>27.549999999999997</v>
+      </c>
+      <c r="H24" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Reprobado/a</v>
+      </c>
+      <c r="I24" s="23"/>
+      <c r="J24" s="24"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="25"/>
       <c r="M24" s="16"/>
     </row>
     <row r="25" spans="1:13" ht="19.45" customHeight="1">
@@ -1489,17 +1742,27 @@
       <c r="C25" s="9">
         <v>57</v>
       </c>
-      <c r="D25" s="9"/>
-      <c r="E25" s="38">
+      <c r="D25" s="9">
+        <v>65</v>
+      </c>
+      <c r="E25" s="9">
         <v>21</v>
       </c>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="20"/>
+      <c r="F25" s="44">
+        <v>45</v>
+      </c>
+      <c r="G25" s="47">
+        <f t="shared" si="0"/>
+        <v>41.4</v>
+      </c>
+      <c r="H25" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Aprobado/a</v>
+      </c>
+      <c r="I25" s="23"/>
+      <c r="J25" s="24"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="25"/>
       <c r="M25" s="16"/>
     </row>
     <row r="26" spans="1:13" ht="19.45" customHeight="1">
@@ -1512,17 +1775,27 @@
       <c r="C26" s="9">
         <v>62</v>
       </c>
-      <c r="D26" s="9"/>
-      <c r="E26" s="38">
+      <c r="D26" s="9">
+        <v>65</v>
+      </c>
+      <c r="E26" s="9">
         <v>25</v>
       </c>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="18"/>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
-      <c r="L26" s="20"/>
+      <c r="F26" s="44">
+        <v>14</v>
+      </c>
+      <c r="G26" s="47">
+        <f t="shared" si="0"/>
+        <v>32.700000000000003</v>
+      </c>
+      <c r="H26" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Examen PES</v>
+      </c>
+      <c r="I26" s="23"/>
+      <c r="J26" s="24"/>
+      <c r="K26" s="24"/>
+      <c r="L26" s="25"/>
       <c r="M26" s="16"/>
     </row>
     <row r="27" spans="1:13" ht="19.45" customHeight="1">
@@ -1535,17 +1808,27 @@
       <c r="C27" s="9">
         <v>70</v>
       </c>
-      <c r="D27" s="9"/>
-      <c r="E27" s="40">
+      <c r="D27" s="9">
+        <v>55</v>
+      </c>
+      <c r="E27" s="19">
         <v>46</v>
       </c>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="18"/>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="20"/>
+      <c r="F27" s="44">
+        <v>34</v>
+      </c>
+      <c r="G27" s="47">
+        <f t="shared" si="0"/>
+        <v>46.749999999999993</v>
+      </c>
+      <c r="H27" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Aprobado/a</v>
+      </c>
+      <c r="I27" s="23"/>
+      <c r="J27" s="24"/>
+      <c r="K27" s="24"/>
+      <c r="L27" s="25"/>
       <c r="M27" s="16"/>
     </row>
     <row r="28" spans="1:13" ht="19.45" customHeight="1">
@@ -1555,16 +1838,30 @@
       <c r="B28" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="18"/>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="20"/>
+      <c r="C28" s="14">
+        <v>10</v>
+      </c>
+      <c r="D28" s="14">
+        <v>30</v>
+      </c>
+      <c r="E28" s="9">
+        <v>10</v>
+      </c>
+      <c r="F28" s="45">
+        <v>10</v>
+      </c>
+      <c r="G28" s="47">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="H28" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Reprobado/a</v>
+      </c>
+      <c r="I28" s="23"/>
+      <c r="J28" s="24"/>
+      <c r="K28" s="24"/>
+      <c r="L28" s="25"/>
       <c r="M28" s="16"/>
     </row>
     <row r="29" spans="1:13" ht="19.45" customHeight="1">
@@ -1577,17 +1874,27 @@
       <c r="C29" s="14">
         <v>70</v>
       </c>
-      <c r="D29" s="14"/>
-      <c r="E29" s="41">
+      <c r="D29" s="14">
+        <v>70</v>
+      </c>
+      <c r="E29" s="20">
         <v>40</v>
       </c>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="18"/>
-      <c r="J29" s="19"/>
-      <c r="K29" s="19"/>
-      <c r="L29" s="20"/>
+      <c r="F29" s="45">
+        <v>70</v>
+      </c>
+      <c r="G29" s="47">
+        <f t="shared" si="0"/>
+        <v>59.5</v>
+      </c>
+      <c r="H29" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Aprobado/a</v>
+      </c>
+      <c r="I29" s="23"/>
+      <c r="J29" s="24"/>
+      <c r="K29" s="24"/>
+      <c r="L29" s="25"/>
       <c r="M29" s="16"/>
     </row>
     <row r="30" spans="1:13" ht="19.45" customHeight="1">
@@ -1600,17 +1907,27 @@
       <c r="C30" s="14">
         <v>60</v>
       </c>
-      <c r="D30" s="14"/>
-      <c r="E30" s="41">
+      <c r="D30" s="14">
+        <v>70</v>
+      </c>
+      <c r="E30" s="20">
         <v>48</v>
       </c>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="18"/>
-      <c r="J30" s="19"/>
-      <c r="K30" s="19"/>
-      <c r="L30" s="20"/>
+      <c r="F30" s="45">
+        <v>65</v>
+      </c>
+      <c r="G30" s="47">
+        <f t="shared" si="0"/>
+        <v>59.05</v>
+      </c>
+      <c r="H30" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Aprobado/a</v>
+      </c>
+      <c r="I30" s="23"/>
+      <c r="J30" s="24"/>
+      <c r="K30" s="24"/>
+      <c r="L30" s="25"/>
       <c r="M30" s="16"/>
     </row>
     <row r="31" spans="1:13" ht="19.45" customHeight="1">
@@ -1623,17 +1940,27 @@
       <c r="C31" s="14">
         <v>70</v>
       </c>
-      <c r="D31" s="14"/>
-      <c r="E31" s="41">
+      <c r="D31" s="14">
+        <v>70</v>
+      </c>
+      <c r="E31" s="20">
         <v>32</v>
       </c>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="18"/>
-      <c r="J31" s="19"/>
-      <c r="K31" s="19"/>
-      <c r="L31" s="20"/>
+      <c r="F31" s="45">
+        <v>70</v>
+      </c>
+      <c r="G31" s="47">
+        <f t="shared" si="0"/>
+        <v>56.7</v>
+      </c>
+      <c r="H31" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Aprobado/a</v>
+      </c>
+      <c r="I31" s="23"/>
+      <c r="J31" s="24"/>
+      <c r="K31" s="24"/>
+      <c r="L31" s="25"/>
       <c r="M31" s="16"/>
     </row>
     <row r="32" spans="1:13" ht="19.45" customHeight="1">
@@ -1645,14 +1972,14 @@
       </c>
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
-      <c r="E32" s="38"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-      <c r="L32" s="20"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="45"/>
+      <c r="G32" s="47"/>
+      <c r="H32" s="48"/>
+      <c r="I32" s="23"/>
+      <c r="J32" s="24"/>
+      <c r="K32" s="24"/>
+      <c r="L32" s="25"/>
       <c r="M32" s="16"/>
     </row>
     <row r="33" spans="1:13" ht="19.45" customHeight="1">
@@ -1665,17 +1992,27 @@
       <c r="C33" s="14">
         <v>65</v>
       </c>
-      <c r="D33" s="14"/>
-      <c r="E33" s="38">
+      <c r="D33" s="14">
+        <v>65</v>
+      </c>
+      <c r="E33" s="9">
         <v>32</v>
       </c>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="18"/>
-      <c r="J33" s="19"/>
-      <c r="K33" s="19"/>
-      <c r="L33" s="20"/>
+      <c r="F33" s="45">
+        <v>49</v>
+      </c>
+      <c r="G33" s="47">
+        <f t="shared" si="0"/>
+        <v>47.849999999999994</v>
+      </c>
+      <c r="H33" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Aprobado/a</v>
+      </c>
+      <c r="I33" s="23"/>
+      <c r="J33" s="24"/>
+      <c r="K33" s="24"/>
+      <c r="L33" s="25"/>
       <c r="M33" s="16"/>
     </row>
     <row r="34" spans="1:13" ht="19.45" customHeight="1">
@@ -1688,17 +2025,27 @@
       <c r="C34" s="9">
         <v>70</v>
       </c>
-      <c r="D34" s="9"/>
-      <c r="E34" s="38">
+      <c r="D34" s="9">
+        <v>70</v>
+      </c>
+      <c r="E34" s="9">
         <v>20</v>
       </c>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="18"/>
-      <c r="J34" s="19"/>
-      <c r="K34" s="19"/>
-      <c r="L34" s="20"/>
+      <c r="F34" s="44">
+        <v>10</v>
+      </c>
+      <c r="G34" s="47">
+        <f t="shared" si="0"/>
+        <v>31.5</v>
+      </c>
+      <c r="H34" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Examen PES</v>
+      </c>
+      <c r="I34" s="23"/>
+      <c r="J34" s="24"/>
+      <c r="K34" s="24"/>
+      <c r="L34" s="25"/>
       <c r="M34" s="16"/>
     </row>
     <row r="35" spans="1:13" ht="19.45" customHeight="1">
@@ -1711,17 +2058,27 @@
       <c r="C35" s="9">
         <v>34</v>
       </c>
-      <c r="D35" s="9"/>
-      <c r="E35" s="42">
+      <c r="D35" s="9">
+        <v>70</v>
+      </c>
+      <c r="E35" s="21">
         <v>40</v>
       </c>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="18"/>
-      <c r="J35" s="19"/>
-      <c r="K35" s="19"/>
-      <c r="L35" s="20"/>
+      <c r="F35" s="44">
+        <v>42</v>
+      </c>
+      <c r="G35" s="47">
+        <f t="shared" si="0"/>
+        <v>44.3</v>
+      </c>
+      <c r="H35" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Aprobado/a</v>
+      </c>
+      <c r="I35" s="23"/>
+      <c r="J35" s="24"/>
+      <c r="K35" s="24"/>
+      <c r="L35" s="25"/>
       <c r="M35" s="16"/>
     </row>
     <row r="36" spans="1:13" ht="19.45" customHeight="1">
@@ -1734,17 +2091,27 @@
       <c r="C36" s="9">
         <v>60</v>
       </c>
-      <c r="D36" s="9"/>
-      <c r="E36" s="38">
+      <c r="D36" s="9">
+        <v>47</v>
+      </c>
+      <c r="E36" s="9">
         <v>55</v>
       </c>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="8"/>
-      <c r="I36" s="18"/>
-      <c r="J36" s="19"/>
-      <c r="K36" s="19"/>
-      <c r="L36" s="20"/>
+      <c r="F36" s="44">
+        <v>48</v>
+      </c>
+      <c r="G36" s="47">
+        <f t="shared" si="0"/>
+        <v>52.099999999999994</v>
+      </c>
+      <c r="H36" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Aprobado/a</v>
+      </c>
+      <c r="I36" s="23"/>
+      <c r="J36" s="24"/>
+      <c r="K36" s="24"/>
+      <c r="L36" s="25"/>
       <c r="M36" s="16"/>
     </row>
     <row r="37" spans="1:13" ht="19.45" customHeight="1">
@@ -1757,17 +2124,27 @@
       <c r="C37" s="17">
         <v>70</v>
       </c>
-      <c r="D37" s="9"/>
-      <c r="E37" s="43">
+      <c r="D37" s="9">
+        <v>65</v>
+      </c>
+      <c r="E37" s="22">
         <v>56</v>
       </c>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="8"/>
-      <c r="I37" s="18"/>
-      <c r="J37" s="19"/>
-      <c r="K37" s="19"/>
-      <c r="L37" s="20"/>
+      <c r="F37" s="44">
+        <v>50</v>
+      </c>
+      <c r="G37" s="47">
+        <f t="shared" si="0"/>
+        <v>57.349999999999994</v>
+      </c>
+      <c r="H37" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Aprobado/a</v>
+      </c>
+      <c r="I37" s="23"/>
+      <c r="J37" s="24"/>
+      <c r="K37" s="24"/>
+      <c r="L37" s="25"/>
       <c r="M37" s="16"/>
     </row>
     <row r="38" spans="1:13" ht="19.45" customHeight="1">
@@ -1780,17 +2157,27 @@
       <c r="C38" s="9">
         <v>30</v>
       </c>
-      <c r="D38" s="9"/>
-      <c r="E38" s="43">
+      <c r="D38" s="9">
+        <v>45</v>
+      </c>
+      <c r="E38" s="22">
         <v>10</v>
       </c>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="8"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="19"/>
-      <c r="K38" s="19"/>
-      <c r="L38" s="20"/>
+      <c r="F38" s="44">
+        <v>10</v>
+      </c>
+      <c r="G38" s="47">
+        <f t="shared" si="0"/>
+        <v>18.25</v>
+      </c>
+      <c r="H38" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Reprobado/a</v>
+      </c>
+      <c r="I38" s="23"/>
+      <c r="J38" s="24"/>
+      <c r="K38" s="24"/>
+      <c r="L38" s="25"/>
       <c r="M38" s="16"/>
     </row>
     <row r="39" spans="1:13" ht="19.45" customHeight="1">
@@ -1803,17 +2190,27 @@
       <c r="C39" s="9">
         <v>70</v>
       </c>
-      <c r="D39" s="9"/>
-      <c r="E39" s="43">
+      <c r="D39" s="9">
+        <v>53</v>
+      </c>
+      <c r="E39" s="22">
         <v>18</v>
       </c>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="8"/>
-      <c r="I39" s="18"/>
-      <c r="J39" s="19"/>
-      <c r="K39" s="19"/>
-      <c r="L39" s="20"/>
+      <c r="F39" s="44">
+        <v>53</v>
+      </c>
+      <c r="G39" s="47">
+        <f t="shared" si="0"/>
+        <v>43.3</v>
+      </c>
+      <c r="H39" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Aprobado/a</v>
+      </c>
+      <c r="I39" s="23"/>
+      <c r="J39" s="24"/>
+      <c r="K39" s="24"/>
+      <c r="L39" s="25"/>
       <c r="M39" s="16"/>
     </row>
     <row r="40" spans="1:13" ht="11.95" customHeight="1"/>
@@ -1823,15 +2220,24 @@
       </c>
       <c r="C41" s="11">
         <f>AVERAGE(C9:C39)</f>
-        <v>60.344827586206897</v>
-      </c>
-      <c r="D41" s="12"/>
+        <v>58.666666666666664</v>
+      </c>
+      <c r="D41" s="11">
+        <f>AVERAGE(D9:D39)</f>
+        <v>56.4</v>
+      </c>
       <c r="E41" s="11">
         <f>AVERAGE(E9:E39)</f>
-        <v>31.964285714285715</v>
-      </c>
-      <c r="F41" s="12"/>
-      <c r="G41" s="12"/>
+        <v>31.206896551724139</v>
+      </c>
+      <c r="F41" s="11">
+        <f>AVERAGE(F9:F39)</f>
+        <v>37.833333333333336</v>
+      </c>
+      <c r="G41" s="49">
+        <f>AVERAGE(G9:G39)</f>
+        <v>41.059999999999988</v>
+      </c>
       <c r="H41" s="12"/>
       <c r="I41" s="12"/>
       <c r="J41" s="12"/>
@@ -2798,28 +3204,6 @@
     <row r="1000" ht="11.95" customHeight="1"/>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="I35:L35"/>
-    <mergeCell ref="I36:L36"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="I33:L33"/>
-    <mergeCell ref="A1:D3"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:I5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:M6"/>
-    <mergeCell ref="I8:L8"/>
-    <mergeCell ref="I9:L9"/>
-    <mergeCell ref="I10:L10"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="I12:L12"/>
     <mergeCell ref="I13:L13"/>
     <mergeCell ref="I26:L26"/>
     <mergeCell ref="I27:L27"/>
@@ -2836,7 +3220,48 @@
     <mergeCell ref="I22:L22"/>
     <mergeCell ref="I23:L23"/>
     <mergeCell ref="I24:L24"/>
+    <mergeCell ref="I8:L8"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="I10:L10"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="A1:D3"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:I5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:M6"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="I35:L35"/>
+    <mergeCell ref="I36:L36"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="I33:L33"/>
   </mergeCells>
+  <conditionalFormatting sqref="G9:G39">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="greaterThanOrEqual">
+      <formula>40</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H9:H39">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Reprobado/a">
+      <formula>NOT(ISERROR(SEARCH("Reprobado/a",H9)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Examen PES">
+      <formula>NOT(ISERROR(SEARCH("Examen PES",H9)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Aprobado/a">
+      <formula>NOT(ISERROR(SEARCH("Aprobado/a",H9)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
   <drawing r:id="rId1"/>

--- a/Calificaciones_1s_2025.xlsx
+++ b/Calificaciones_1s_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Omar\Documents\Cursos\Física Computacional III para Astrofísica\2025_1s\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4C36BA7-CE02-493D-9C00-442424B913DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2791DED0-98FB-4992-BC30-46B9AE3116D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-104" yWindow="-104" windowWidth="22326" windowHeight="12050" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -668,11 +668,37 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -695,32 +721,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -730,11 +730,14 @@
     <cellStyle name="Normal 5" xfId="4" xr:uid="{2C655FE6-0C66-40EF-AB21-F1FDA2CBF38B}"/>
     <cellStyle name="Normal 6" xfId="5" xr:uid="{8502967F-F2F6-4CD0-9005-23248AD21CC2}"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="5">
     <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFEE0000"/>
+          <bgColor rgb="FF00E668"/>
         </patternFill>
       </fill>
     </dxf>
@@ -749,27 +752,9 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FF00E668"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFEE0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
+          <bgColor rgb="FFEE0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1057,10 +1042,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="39.75" customHeight="1">
-      <c r="A1" s="26"/>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="28"/>
+      <c r="A1" s="36"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="38"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -1072,27 +1057,27 @@
       <c r="M1" s="1"/>
     </row>
     <row r="2" spans="1:13" ht="19.45" customHeight="1">
-      <c r="A2" s="29"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="31"/>
+      <c r="A2" s="39"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="41"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-      <c r="I2" s="35" t="s">
+      <c r="I2" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="36"/>
-      <c r="K2" s="37"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="47"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" ht="3.75" customHeight="1">
-      <c r="A3" s="32"/>
-      <c r="B3" s="33"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="34"/>
+      <c r="A3" s="42"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="44"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
@@ -1119,19 +1104,19 @@
       <c r="M4" s="1"/>
     </row>
     <row r="5" spans="1:13" ht="15.7" customHeight="1">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="39" t="s">
+      <c r="B5" s="47"/>
+      <c r="C5" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="37"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="47"/>
       <c r="J5" s="2" t="s">
         <v>3</v>
       </c>
@@ -1142,23 +1127,23 @@
       <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:13" ht="15.7" customHeight="1">
-      <c r="A6" s="38" t="s">
+      <c r="A6" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="37"/>
-      <c r="C6" s="39" t="s">
+      <c r="B6" s="47"/>
+      <c r="C6" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="36"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="36"/>
-      <c r="M6" s="37"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46"/>
+      <c r="J6" s="46"/>
+      <c r="K6" s="46"/>
+      <c r="L6" s="46"/>
+      <c r="M6" s="47"/>
     </row>
     <row r="7" spans="1:13" ht="4.5" customHeight="1">
       <c r="A7" s="1"/>
@@ -1191,19 +1176,19 @@
       <c r="E8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="43" t="s">
+      <c r="F8" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="46" t="s">
+      <c r="G8" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="46" t="s">
+      <c r="H8" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="I8" s="40"/>
-      <c r="J8" s="41"/>
-      <c r="K8" s="41"/>
-      <c r="L8" s="42"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="34"/>
+      <c r="L8" s="35"/>
       <c r="M8" s="16"/>
     </row>
     <row r="9" spans="1:13" ht="19.45" customHeight="1">
@@ -1222,21 +1207,21 @@
       <c r="E9" s="9">
         <v>34</v>
       </c>
-      <c r="F9" s="44">
+      <c r="F9" s="24">
         <v>11</v>
       </c>
-      <c r="G9" s="47">
+      <c r="G9" s="27">
         <f>0.3*(C9+D9)/2+0.35*E9+0.35*F9</f>
         <v>33</v>
       </c>
-      <c r="H9" s="48" t="str">
+      <c r="H9" s="28" t="str">
         <f>IF(G9&gt;=40,"Aprobado/a",IF(G9&gt;=30,"Examen PES","Reprobado/a"))</f>
         <v>Examen PES</v>
       </c>
-      <c r="I9" s="23"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="24"/>
-      <c r="L9" s="25"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="32"/>
       <c r="M9" s="16"/>
     </row>
     <row r="10" spans="1:13" ht="19.45" customHeight="1">
@@ -1255,21 +1240,21 @@
       <c r="E10" s="9">
         <v>13</v>
       </c>
-      <c r="F10" s="44">
+      <c r="F10" s="24">
         <v>12</v>
       </c>
-      <c r="G10" s="47">
+      <c r="G10" s="27">
         <f t="shared" ref="G10:G39" si="0">0.3*(C10+D10)/2+0.35*E10+0.35*F10</f>
         <v>15.799999999999999</v>
       </c>
-      <c r="H10" s="48" t="str">
+      <c r="H10" s="28" t="str">
         <f t="shared" ref="H10:H39" si="1">IF(G10&gt;=40,"Aprobado/a",IF(G10&gt;=30,"Examen PES","Reprobado/a"))</f>
         <v>Reprobado/a</v>
       </c>
-      <c r="I10" s="23"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="25"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="32"/>
       <c r="M10" s="16"/>
     </row>
     <row r="11" spans="1:13" ht="19.45" customHeight="1">
@@ -1288,21 +1273,21 @@
       <c r="E11" s="9">
         <v>54</v>
       </c>
-      <c r="F11" s="45">
+      <c r="F11" s="25">
         <v>57</v>
       </c>
-      <c r="G11" s="47">
+      <c r="G11" s="27">
         <f t="shared" si="0"/>
         <v>56.55</v>
       </c>
-      <c r="H11" s="48" t="str">
+      <c r="H11" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Aprobado/a</v>
       </c>
-      <c r="I11" s="23"/>
-      <c r="J11" s="24"/>
-      <c r="K11" s="24"/>
-      <c r="L11" s="25"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="32"/>
       <c r="M11" s="16"/>
     </row>
     <row r="12" spans="1:13" ht="19.45" customHeight="1">
@@ -1321,21 +1306,21 @@
       <c r="E12" s="9">
         <v>33</v>
       </c>
-      <c r="F12" s="44">
+      <c r="F12" s="24">
         <v>40</v>
       </c>
-      <c r="G12" s="47">
+      <c r="G12" s="27">
         <f t="shared" si="0"/>
         <v>45.05</v>
       </c>
-      <c r="H12" s="48" t="str">
+      <c r="H12" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Aprobado/a</v>
       </c>
-      <c r="I12" s="23"/>
-      <c r="J12" s="24"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="25"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="32"/>
       <c r="M12" s="16"/>
     </row>
     <row r="13" spans="1:13" ht="19.45" customHeight="1">
@@ -1354,21 +1339,21 @@
       <c r="E13" s="9">
         <v>40</v>
       </c>
-      <c r="F13" s="44">
+      <c r="F13" s="24">
         <v>37</v>
       </c>
-      <c r="G13" s="47">
+      <c r="G13" s="27">
         <f t="shared" si="0"/>
         <v>43.45</v>
       </c>
-      <c r="H13" s="48" t="str">
+      <c r="H13" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Aprobado/a</v>
       </c>
-      <c r="I13" s="23"/>
-      <c r="J13" s="24"/>
-      <c r="K13" s="24"/>
-      <c r="L13" s="25"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="31"/>
+      <c r="K13" s="31"/>
+      <c r="L13" s="32"/>
       <c r="M13" s="16"/>
     </row>
     <row r="14" spans="1:13" ht="19.45" customHeight="1">
@@ -1387,21 +1372,21 @@
       <c r="E14" s="9">
         <v>26</v>
       </c>
-      <c r="F14" s="44">
+      <c r="F14" s="24">
         <v>28</v>
       </c>
-      <c r="G14" s="47">
+      <c r="G14" s="27">
         <f t="shared" si="0"/>
         <v>33.15</v>
       </c>
-      <c r="H14" s="48" t="str">
+      <c r="H14" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Examen PES</v>
       </c>
-      <c r="I14" s="23"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="25"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="31"/>
+      <c r="K14" s="31"/>
+      <c r="L14" s="32"/>
       <c r="M14" s="16"/>
     </row>
     <row r="15" spans="1:13" ht="19.45" customHeight="1">
@@ -1420,21 +1405,21 @@
       <c r="E15" s="18">
         <v>34</v>
       </c>
-      <c r="F15" s="44">
+      <c r="F15" s="24">
         <v>46</v>
       </c>
-      <c r="G15" s="47">
+      <c r="G15" s="27">
         <f t="shared" si="0"/>
         <v>48.55</v>
       </c>
-      <c r="H15" s="48" t="str">
+      <c r="H15" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Aprobado/a</v>
       </c>
-      <c r="I15" s="23"/>
-      <c r="J15" s="24"/>
-      <c r="K15" s="24"/>
-      <c r="L15" s="25"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="31"/>
+      <c r="L15" s="32"/>
       <c r="M15" s="16"/>
     </row>
     <row r="16" spans="1:13" ht="19.45" customHeight="1">
@@ -1453,21 +1438,21 @@
       <c r="E16" s="18">
         <v>22</v>
       </c>
-      <c r="F16" s="44">
+      <c r="F16" s="24">
         <v>50</v>
       </c>
-      <c r="G16" s="47">
+      <c r="G16" s="27">
         <f t="shared" si="0"/>
         <v>43.2</v>
       </c>
-      <c r="H16" s="48" t="str">
+      <c r="H16" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Aprobado/a</v>
       </c>
-      <c r="I16" s="23"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="25"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="31"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="32"/>
       <c r="M16" s="16"/>
     </row>
     <row r="17" spans="1:13" ht="19.45" customHeight="1">
@@ -1486,21 +1471,21 @@
       <c r="E17" s="18">
         <v>38</v>
       </c>
-      <c r="F17" s="44">
+      <c r="F17" s="24">
         <v>49</v>
       </c>
-      <c r="G17" s="47">
+      <c r="G17" s="27">
         <f t="shared" si="0"/>
         <v>50.699999999999996</v>
       </c>
-      <c r="H17" s="48" t="str">
+      <c r="H17" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Aprobado/a</v>
       </c>
-      <c r="I17" s="23"/>
-      <c r="J17" s="24"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="25"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="32"/>
       <c r="M17" s="16"/>
     </row>
     <row r="18" spans="1:13" ht="19.45" customHeight="1">
@@ -1519,21 +1504,21 @@
       <c r="E18" s="18">
         <v>36</v>
       </c>
-      <c r="F18" s="44">
+      <c r="F18" s="24">
         <v>55</v>
       </c>
-      <c r="G18" s="47">
+      <c r="G18" s="27">
         <f t="shared" si="0"/>
         <v>51.8</v>
       </c>
-      <c r="H18" s="48" t="str">
+      <c r="H18" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Aprobado/a</v>
       </c>
-      <c r="I18" s="23"/>
-      <c r="J18" s="24"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="25"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="31"/>
+      <c r="K18" s="31"/>
+      <c r="L18" s="32"/>
       <c r="M18" s="16"/>
     </row>
     <row r="19" spans="1:13" ht="19.45" customHeight="1">
@@ -1552,21 +1537,21 @@
       <c r="E19" s="9">
         <v>14</v>
       </c>
-      <c r="F19" s="44">
+      <c r="F19" s="24">
         <v>12</v>
       </c>
-      <c r="G19" s="47">
+      <c r="G19" s="27">
         <f t="shared" si="0"/>
         <v>23.349999999999998</v>
       </c>
-      <c r="H19" s="48" t="str">
+      <c r="H19" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Reprobado/a</v>
       </c>
-      <c r="I19" s="23"/>
-      <c r="J19" s="24"/>
-      <c r="K19" s="24"/>
-      <c r="L19" s="25"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="31"/>
+      <c r="K19" s="31"/>
+      <c r="L19" s="32"/>
       <c r="M19" s="16"/>
     </row>
     <row r="20" spans="1:13" ht="19.45" customHeight="1">
@@ -1582,22 +1567,24 @@
       <c r="D20" s="9">
         <v>58</v>
       </c>
-      <c r="E20" s="9"/>
-      <c r="F20" s="44">
+      <c r="E20" s="9">
+        <v>10</v>
+      </c>
+      <c r="F20" s="24">
         <v>12</v>
       </c>
-      <c r="G20" s="47">
+      <c r="G20" s="27">
         <f t="shared" si="0"/>
-        <v>21.9</v>
-      </c>
-      <c r="H20" s="48" t="str">
+        <v>25.4</v>
+      </c>
+      <c r="H20" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Reprobado/a</v>
       </c>
-      <c r="I20" s="23"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="24"/>
-      <c r="L20" s="25"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="31"/>
+      <c r="K20" s="31"/>
+      <c r="L20" s="32"/>
       <c r="M20" s="16"/>
     </row>
     <row r="21" spans="1:13" ht="19.45" customHeight="1">
@@ -1616,21 +1603,21 @@
       <c r="E21" s="9">
         <v>44</v>
       </c>
-      <c r="F21" s="44">
+      <c r="F21" s="24">
         <v>51</v>
       </c>
-      <c r="G21" s="47">
+      <c r="G21" s="27">
         <f t="shared" si="0"/>
         <v>53.949999999999989</v>
       </c>
-      <c r="H21" s="48" t="str">
+      <c r="H21" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Aprobado/a</v>
       </c>
-      <c r="I21" s="23"/>
-      <c r="J21" s="24"/>
-      <c r="K21" s="24"/>
-      <c r="L21" s="25"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
+      <c r="L21" s="32"/>
       <c r="M21" s="16"/>
     </row>
     <row r="22" spans="1:13" ht="19.45" customHeight="1">
@@ -1649,21 +1636,21 @@
       <c r="E22" s="9">
         <v>26</v>
       </c>
-      <c r="F22" s="44">
+      <c r="F22" s="24">
         <v>33</v>
       </c>
-      <c r="G22" s="47">
+      <c r="G22" s="27">
         <f t="shared" si="0"/>
         <v>35.5</v>
       </c>
-      <c r="H22" s="48" t="str">
+      <c r="H22" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Examen PES</v>
       </c>
-      <c r="I22" s="23"/>
-      <c r="J22" s="24"/>
-      <c r="K22" s="24"/>
-      <c r="L22" s="25"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="32"/>
       <c r="M22" s="16"/>
     </row>
     <row r="23" spans="1:13" ht="19.45" customHeight="1">
@@ -1682,21 +1669,21 @@
       <c r="E23" s="9">
         <v>28</v>
       </c>
-      <c r="F23" s="44">
+      <c r="F23" s="24">
         <v>47</v>
       </c>
-      <c r="G23" s="47">
+      <c r="G23" s="27">
         <f t="shared" si="0"/>
         <v>44.55</v>
       </c>
-      <c r="H23" s="48" t="str">
+      <c r="H23" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Aprobado/a</v>
       </c>
-      <c r="I23" s="23"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="25"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="32"/>
       <c r="M23" s="16"/>
     </row>
     <row r="24" spans="1:13" ht="19.45" customHeight="1">
@@ -1715,21 +1702,21 @@
       <c r="E24" s="9">
         <v>10</v>
       </c>
-      <c r="F24" s="44">
+      <c r="F24" s="24">
         <v>25</v>
       </c>
-      <c r="G24" s="47">
+      <c r="G24" s="27">
         <f t="shared" si="0"/>
         <v>27.549999999999997</v>
       </c>
-      <c r="H24" s="48" t="str">
+      <c r="H24" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Reprobado/a</v>
       </c>
-      <c r="I24" s="23"/>
-      <c r="J24" s="24"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="25"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="32"/>
       <c r="M24" s="16"/>
     </row>
     <row r="25" spans="1:13" ht="19.45" customHeight="1">
@@ -1748,21 +1735,21 @@
       <c r="E25" s="9">
         <v>21</v>
       </c>
-      <c r="F25" s="44">
+      <c r="F25" s="24">
         <v>45</v>
       </c>
-      <c r="G25" s="47">
+      <c r="G25" s="27">
         <f t="shared" si="0"/>
         <v>41.4</v>
       </c>
-      <c r="H25" s="48" t="str">
+      <c r="H25" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Aprobado/a</v>
       </c>
-      <c r="I25" s="23"/>
-      <c r="J25" s="24"/>
-      <c r="K25" s="24"/>
-      <c r="L25" s="25"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="32"/>
       <c r="M25" s="16"/>
     </row>
     <row r="26" spans="1:13" ht="19.45" customHeight="1">
@@ -1781,21 +1768,21 @@
       <c r="E26" s="9">
         <v>25</v>
       </c>
-      <c r="F26" s="44">
+      <c r="F26" s="24">
         <v>14</v>
       </c>
-      <c r="G26" s="47">
+      <c r="G26" s="27">
         <f t="shared" si="0"/>
         <v>32.700000000000003</v>
       </c>
-      <c r="H26" s="48" t="str">
+      <c r="H26" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Examen PES</v>
       </c>
-      <c r="I26" s="23"/>
-      <c r="J26" s="24"/>
-      <c r="K26" s="24"/>
-      <c r="L26" s="25"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="32"/>
       <c r="M26" s="16"/>
     </row>
     <row r="27" spans="1:13" ht="19.45" customHeight="1">
@@ -1814,21 +1801,21 @@
       <c r="E27" s="19">
         <v>46</v>
       </c>
-      <c r="F27" s="44">
+      <c r="F27" s="24">
         <v>34</v>
       </c>
-      <c r="G27" s="47">
+      <c r="G27" s="27">
         <f t="shared" si="0"/>
         <v>46.749999999999993</v>
       </c>
-      <c r="H27" s="48" t="str">
+      <c r="H27" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Aprobado/a</v>
       </c>
-      <c r="I27" s="23"/>
-      <c r="J27" s="24"/>
-      <c r="K27" s="24"/>
-      <c r="L27" s="25"/>
+      <c r="I27" s="30"/>
+      <c r="J27" s="31"/>
+      <c r="K27" s="31"/>
+      <c r="L27" s="32"/>
       <c r="M27" s="16"/>
     </row>
     <row r="28" spans="1:13" ht="19.45" customHeight="1">
@@ -1847,21 +1834,21 @@
       <c r="E28" s="9">
         <v>10</v>
       </c>
-      <c r="F28" s="45">
+      <c r="F28" s="25">
         <v>10</v>
       </c>
-      <c r="G28" s="47">
+      <c r="G28" s="27">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="H28" s="48" t="str">
+      <c r="H28" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Reprobado/a</v>
       </c>
-      <c r="I28" s="23"/>
-      <c r="J28" s="24"/>
-      <c r="K28" s="24"/>
-      <c r="L28" s="25"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="32"/>
       <c r="M28" s="16"/>
     </row>
     <row r="29" spans="1:13" ht="19.45" customHeight="1">
@@ -1880,21 +1867,21 @@
       <c r="E29" s="20">
         <v>40</v>
       </c>
-      <c r="F29" s="45">
+      <c r="F29" s="25">
         <v>70</v>
       </c>
-      <c r="G29" s="47">
+      <c r="G29" s="27">
         <f t="shared" si="0"/>
         <v>59.5</v>
       </c>
-      <c r="H29" s="48" t="str">
+      <c r="H29" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Aprobado/a</v>
       </c>
-      <c r="I29" s="23"/>
-      <c r="J29" s="24"/>
-      <c r="K29" s="24"/>
-      <c r="L29" s="25"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="31"/>
+      <c r="K29" s="31"/>
+      <c r="L29" s="32"/>
       <c r="M29" s="16"/>
     </row>
     <row r="30" spans="1:13" ht="19.45" customHeight="1">
@@ -1913,21 +1900,21 @@
       <c r="E30" s="20">
         <v>48</v>
       </c>
-      <c r="F30" s="45">
+      <c r="F30" s="25">
         <v>65</v>
       </c>
-      <c r="G30" s="47">
+      <c r="G30" s="27">
         <f t="shared" si="0"/>
         <v>59.05</v>
       </c>
-      <c r="H30" s="48" t="str">
+      <c r="H30" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Aprobado/a</v>
       </c>
-      <c r="I30" s="23"/>
-      <c r="J30" s="24"/>
-      <c r="K30" s="24"/>
-      <c r="L30" s="25"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="31"/>
+      <c r="K30" s="31"/>
+      <c r="L30" s="32"/>
       <c r="M30" s="16"/>
     </row>
     <row r="31" spans="1:13" ht="19.45" customHeight="1">
@@ -1946,21 +1933,21 @@
       <c r="E31" s="20">
         <v>32</v>
       </c>
-      <c r="F31" s="45">
+      <c r="F31" s="25">
         <v>70</v>
       </c>
-      <c r="G31" s="47">
+      <c r="G31" s="27">
         <f t="shared" si="0"/>
         <v>56.7</v>
       </c>
-      <c r="H31" s="48" t="str">
+      <c r="H31" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Aprobado/a</v>
       </c>
-      <c r="I31" s="23"/>
-      <c r="J31" s="24"/>
-      <c r="K31" s="24"/>
-      <c r="L31" s="25"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="31"/>
+      <c r="K31" s="31"/>
+      <c r="L31" s="32"/>
       <c r="M31" s="16"/>
     </row>
     <row r="32" spans="1:13" ht="19.45" customHeight="1">
@@ -1973,13 +1960,13 @@
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
       <c r="E32" s="9"/>
-      <c r="F32" s="45"/>
-      <c r="G32" s="47"/>
-      <c r="H32" s="48"/>
-      <c r="I32" s="23"/>
-      <c r="J32" s="24"/>
-      <c r="K32" s="24"/>
-      <c r="L32" s="25"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="31"/>
+      <c r="K32" s="31"/>
+      <c r="L32" s="32"/>
       <c r="M32" s="16"/>
     </row>
     <row r="33" spans="1:13" ht="19.45" customHeight="1">
@@ -1998,21 +1985,21 @@
       <c r="E33" s="9">
         <v>32</v>
       </c>
-      <c r="F33" s="45">
+      <c r="F33" s="25">
         <v>49</v>
       </c>
-      <c r="G33" s="47">
+      <c r="G33" s="27">
         <f t="shared" si="0"/>
         <v>47.849999999999994</v>
       </c>
-      <c r="H33" s="48" t="str">
+      <c r="H33" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Aprobado/a</v>
       </c>
-      <c r="I33" s="23"/>
-      <c r="J33" s="24"/>
-      <c r="K33" s="24"/>
-      <c r="L33" s="25"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="32"/>
       <c r="M33" s="16"/>
     </row>
     <row r="34" spans="1:13" ht="19.45" customHeight="1">
@@ -2031,21 +2018,21 @@
       <c r="E34" s="9">
         <v>20</v>
       </c>
-      <c r="F34" s="44">
+      <c r="F34" s="24">
         <v>10</v>
       </c>
-      <c r="G34" s="47">
+      <c r="G34" s="27">
         <f t="shared" si="0"/>
         <v>31.5</v>
       </c>
-      <c r="H34" s="48" t="str">
+      <c r="H34" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Examen PES</v>
       </c>
-      <c r="I34" s="23"/>
-      <c r="J34" s="24"/>
-      <c r="K34" s="24"/>
-      <c r="L34" s="25"/>
+      <c r="I34" s="30"/>
+      <c r="J34" s="31"/>
+      <c r="K34" s="31"/>
+      <c r="L34" s="32"/>
       <c r="M34" s="16"/>
     </row>
     <row r="35" spans="1:13" ht="19.45" customHeight="1">
@@ -2064,21 +2051,21 @@
       <c r="E35" s="21">
         <v>40</v>
       </c>
-      <c r="F35" s="44">
+      <c r="F35" s="24">
         <v>42</v>
       </c>
-      <c r="G35" s="47">
+      <c r="G35" s="27">
         <f t="shared" si="0"/>
         <v>44.3</v>
       </c>
-      <c r="H35" s="48" t="str">
+      <c r="H35" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Aprobado/a</v>
       </c>
-      <c r="I35" s="23"/>
-      <c r="J35" s="24"/>
-      <c r="K35" s="24"/>
-      <c r="L35" s="25"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="31"/>
+      <c r="K35" s="31"/>
+      <c r="L35" s="32"/>
       <c r="M35" s="16"/>
     </row>
     <row r="36" spans="1:13" ht="19.45" customHeight="1">
@@ -2097,21 +2084,21 @@
       <c r="E36" s="9">
         <v>55</v>
       </c>
-      <c r="F36" s="44">
+      <c r="F36" s="24">
         <v>48</v>
       </c>
-      <c r="G36" s="47">
+      <c r="G36" s="27">
         <f t="shared" si="0"/>
         <v>52.099999999999994</v>
       </c>
-      <c r="H36" s="48" t="str">
+      <c r="H36" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Aprobado/a</v>
       </c>
-      <c r="I36" s="23"/>
-      <c r="J36" s="24"/>
-      <c r="K36" s="24"/>
-      <c r="L36" s="25"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="31"/>
+      <c r="K36" s="31"/>
+      <c r="L36" s="32"/>
       <c r="M36" s="16"/>
     </row>
     <row r="37" spans="1:13" ht="19.45" customHeight="1">
@@ -2130,21 +2117,21 @@
       <c r="E37" s="22">
         <v>56</v>
       </c>
-      <c r="F37" s="44">
+      <c r="F37" s="24">
         <v>50</v>
       </c>
-      <c r="G37" s="47">
+      <c r="G37" s="27">
         <f t="shared" si="0"/>
         <v>57.349999999999994</v>
       </c>
-      <c r="H37" s="48" t="str">
+      <c r="H37" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Aprobado/a</v>
       </c>
-      <c r="I37" s="23"/>
-      <c r="J37" s="24"/>
-      <c r="K37" s="24"/>
-      <c r="L37" s="25"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="31"/>
+      <c r="K37" s="31"/>
+      <c r="L37" s="32"/>
       <c r="M37" s="16"/>
     </row>
     <row r="38" spans="1:13" ht="19.45" customHeight="1">
@@ -2163,21 +2150,21 @@
       <c r="E38" s="22">
         <v>10</v>
       </c>
-      <c r="F38" s="44">
+      <c r="F38" s="24">
         <v>10</v>
       </c>
-      <c r="G38" s="47">
+      <c r="G38" s="27">
         <f t="shared" si="0"/>
         <v>18.25</v>
       </c>
-      <c r="H38" s="48" t="str">
+      <c r="H38" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Reprobado/a</v>
       </c>
-      <c r="I38" s="23"/>
-      <c r="J38" s="24"/>
-      <c r="K38" s="24"/>
-      <c r="L38" s="25"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="31"/>
+      <c r="K38" s="31"/>
+      <c r="L38" s="32"/>
       <c r="M38" s="16"/>
     </row>
     <row r="39" spans="1:13" ht="19.45" customHeight="1">
@@ -2196,21 +2183,21 @@
       <c r="E39" s="22">
         <v>18</v>
       </c>
-      <c r="F39" s="44">
+      <c r="F39" s="24">
         <v>53</v>
       </c>
-      <c r="G39" s="47">
+      <c r="G39" s="27">
         <f t="shared" si="0"/>
         <v>43.3</v>
       </c>
-      <c r="H39" s="48" t="str">
+      <c r="H39" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Aprobado/a</v>
       </c>
-      <c r="I39" s="23"/>
-      <c r="J39" s="24"/>
-      <c r="K39" s="24"/>
-      <c r="L39" s="25"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="31"/>
+      <c r="K39" s="31"/>
+      <c r="L39" s="32"/>
       <c r="M39" s="16"/>
     </row>
     <row r="40" spans="1:13" ht="11.95" customHeight="1"/>
@@ -2228,15 +2215,15 @@
       </c>
       <c r="E41" s="11">
         <f>AVERAGE(E9:E39)</f>
-        <v>31.206896551724139</v>
+        <v>30.5</v>
       </c>
       <c r="F41" s="11">
         <f>AVERAGE(F9:F39)</f>
         <v>37.833333333333336</v>
       </c>
-      <c r="G41" s="49">
+      <c r="G41" s="29">
         <f>AVERAGE(G9:G39)</f>
-        <v>41.059999999999988</v>
+        <v>41.176666666666655</v>
       </c>
       <c r="H41" s="12"/>
       <c r="I41" s="12"/>
@@ -3204,6 +3191,28 @@
     <row r="1000" ht="11.95" customHeight="1"/>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="I35:L35"/>
+    <mergeCell ref="I36:L36"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="I33:L33"/>
+    <mergeCell ref="A1:D3"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:I5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:M6"/>
+    <mergeCell ref="I8:L8"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="I10:L10"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="I12:L12"/>
     <mergeCell ref="I13:L13"/>
     <mergeCell ref="I26:L26"/>
     <mergeCell ref="I27:L27"/>
@@ -3220,45 +3229,23 @@
     <mergeCell ref="I22:L22"/>
     <mergeCell ref="I23:L23"/>
     <mergeCell ref="I24:L24"/>
-    <mergeCell ref="I8:L8"/>
-    <mergeCell ref="I9:L9"/>
-    <mergeCell ref="I10:L10"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="A1:D3"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:I5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:M6"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="I35:L35"/>
-    <mergeCell ref="I36:L36"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="I33:L33"/>
   </mergeCells>
   <conditionalFormatting sqref="G9:G39">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="greaterThanOrEqual">
       <formula>40</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9:H39">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Reprobado/a">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="Reprobado/a">
       <formula>NOT(ISERROR(SEARCH("Reprobado/a",H9)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Examen PES">
       <formula>NOT(ISERROR(SEARCH("Examen PES",H9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Aprobado/a">
+    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="Aprobado/a">
       <formula>NOT(ISERROR(SEARCH("Aprobado/a",H9)))</formula>
     </cfRule>
   </conditionalFormatting>
